--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -129,7 +129,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Q1</t>
+    <t>Q1a</t>
   </si>
   <si>
     <t>Diodes Inc</t>
@@ -168,7 +168,7 @@
     <t>R15</t>
   </si>
   <si>
-    <t>Susumu</t>
+    <t>Susumua</t>
   </si>
   <si>
     <t>RL3720WT-R022-F</t>

--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -1292,7 +1292,9 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>

--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -1305,7 +1305,9 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>

--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -1305,9 +1305,7 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>

--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -129,7 +129,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Q1a</t>
+    <t>Q1</t>
   </si>
   <si>
     <t>Diodes Inc</t>
@@ -168,7 +168,7 @@
     <t>R15</t>
   </si>
   <si>
-    <t>Susumua</t>
+    <t>Susumu</t>
   </si>
   <si>
     <t>RL3720WT-R022-F</t>
@@ -1305,7 +1305,9 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>

--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -1247,9 +1247,7 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>1</v>
-      </c>
+      <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>
@@ -1260,9 +1258,7 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>2</v>
-      </c>
+      <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>

--- a/test_data/new.xlsx
+++ b/test_data/new.xlsx
@@ -1089,8 +1089,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+    </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>80</v>
